--- a/jogos_2025-01-16.xlsx
+++ b/jogos_2025-01-16.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Raed</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>5.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['21', '45+7', '71', '77']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45673.58333333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Raed</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['21', '45+7', '71', '77']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>4</v>
-      </c>
       <c r="AI8" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45673.58333333334</v>
